--- a/output/2026-10-04_18_Malesia_Selangor_Cleaning.xlsx
+++ b/output/2026-10-04_18_Malesia_Selangor_Cleaning.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dal 1996, distributore di spazzatrici industriali/stradali/aeroportuali e attrezzature aspirazione. Rappresenta Bucher Municipal, Hako, PowerBoss, Etesia, SIDES, Disab, Energreen, BEAM. Verificato via sito ufficiale.</t>
+          <t>Dal 1996, distributore di spazzatrici industriali/stradali/aeroportuali e attrezzature aspirazione. Rappresenta Bucher Municipal, Hako, PowerBoss, Etesia, SIDES, Disab, Energreen, BEAM. Verificato via sito ufficiale. [DUPLICATO — vedi anche: 2026-10-02_17_Malesia_Pahang_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -516,7 +516,6 @@
           <t>Klenco (M) Sdn Bhd</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>Shah Alam (Seksyen 32), Selangor</t>
@@ -527,11 +526,9 @@
           <t>Cleaning</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dal 1971, distributore indipendente di macchine/utensili/chimici per pulizia istituzionale/industriale/municipale nel SE Asia (~30.000 referenze). Esistenza confermata da fonti terze (directory aziendali, portali lavoro); sito non raggiungibile, telefono/email non reperiti da fonte verificabile.</t>
+          <t>Dal 1971, distributore indipendente di macchine/utensili/chimici per pulizia istituzionale/industriale/municipale nel SE Asia (~30.000 referenze). Esistenza confermata da fonti terze (directory aziendali, portali lavoro); sito non raggiungibile, telefono/email non reperiti da fonte verificabile. [DUPLICATO — vedi anche: 2026-10-02_17_Malesia_Pahang_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -546,7 +543,6 @@
           <t>Floormac (M) Sdn Bhd</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>Subang Jaya, Selangor</t>
@@ -557,11 +553,9 @@
           <t>Cleaning</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Importatore/distributore di attrezzature professionali per pulizia pavimenti, heavy duty cleaning equipment e chimici per pulizia, con servizio riparazione. Esistenza confermata (SSM 201801018274, directory aziendali, offerte di lavoro). Telefono/email non reperiti da fonte verificabile.</t>
+          <t>Importatore/distributore di attrezzature professionali per pulizia pavimenti, heavy duty cleaning equipment e chimici per pulizia, con servizio riparazione. Esistenza confermata (SSM 201801018274, directory aziendali, offerte di lavoro). Telefono/email non reperiti da fonte verificabile. [DUPLICATO — vedi anche: 2026-10-02_17_Malesia_Pahang_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -603,7 +597,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Filiale malese del produttore Kärcher. Vende idropulitrici, lavapavimenti, aspiratori industriali. Verificato via sito ufficiale.</t>
+          <t>Filiale malese del produttore Kärcher. Vende idropulitrici, lavapavimenti, aspiratori industriali. Verificato via sito ufficiale. [DUPLICATO — vedi anche: 2026-10-02_17_Malesia_Pahang_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -645,7 +639,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dal 1992, fornitore soluzioni igieniche commerciali/industriali: scrubber, aspiratori, spazzatrici, lucidatrici, chimici, sistemi mopping/washroom. Filiali a Melaka e Kuantan. Verificato via sito ufficiale.</t>
+          <t>Dal 1992, fornitore soluzioni igieniche commerciali/industriali: scrubber, aspiratori, spazzatrici, lucidatrici, chimici, sistemi mopping/washroom. Filiali a Melaka e Kuantan. Verificato via sito ufficiale. [DUPLICATO — vedi anche: 2026-10-01_21_Malesia_Melaka_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -687,7 +681,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rivenditore multi-categoria utensili/sicurezza con linea "Cleaning &amp; Vacuum Tools". Verificato via sito ufficiale, SSM 200601035792.</t>
+          <t>Rivenditore multi-categoria utensili/sicurezza con linea "Cleaning &amp; Vacuum Tools". Verificato via sito ufficiale, SSM 200601035792. [DUPLICATO — vedi anche: 2026-10-03_11_Malesia_Perlis_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -702,7 +696,6 @@
           <t>Chempro Technology (M) Sdn Bhd</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>Klang, Selangor</t>
@@ -713,8 +706,6 @@
           <t>Cleaning</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>BORDERLINE: produttore/fornitore proprio di chimici specialistici per pulizia industriale/manifatturiera (non rivenditore multi-brand di macchine). 51-100 dipendenti, certificazioni ISO. Contatti non reperiti da fonte verificabile. Valutare in revisione umana se rientra nel perimetro.</t>
@@ -722,7 +713,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
